--- a/docentes/Rivera Serra Alma Lilian - Estadisticos 20211.xlsx
+++ b/docentes/Rivera Serra Alma Lilian - Estadisticos 20211.xlsx
@@ -562,16 +562,19 @@
         <v>31</v>
       </c>
       <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
         <v>31</v>
       </c>
-      <c r="E2">
-        <v>31</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
       <c r="G2">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H2">
+        <v>7.7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -585,16 +588,19 @@
         <v>34</v>
       </c>
       <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
         <v>34</v>
       </c>
-      <c r="E3">
-        <v>34</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
       <c r="G3">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H3">
+        <v>8.6</v>
       </c>
     </row>
   </sheetData>
@@ -659,7 +665,7 @@
         <v>100</v>
       </c>
       <c r="H2">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="3" spans="1:8">

--- a/docentes/Rivera Serra Alma Lilian - Estadisticos 20211.xlsx
+++ b/docentes/Rivera Serra Alma Lilian - Estadisticos 20211.xlsx
@@ -665,7 +665,7 @@
         <v>100</v>
       </c>
       <c r="H2">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -691,7 +691,7 @@
         <v>100</v>
       </c>
       <c r="H3">
-        <v>8.6</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
   </sheetData>
